--- a/Analisis extrapolación.xlsx
+++ b/Analisis extrapolación.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\Python Script\Github\IBNR-NIIF-17\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Python_script\Github\IBNR-NIIF-17\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE926036-53E6-4957-9E65-522FF81057F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FEB576-8E04-4351-BD11-E3E36EC5F288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RC Cosas" sheetId="1" r:id="rId1"/>
@@ -336,67 +336,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>1.1994341194934199</c:v>
+                  <c:v>1.1944551199766771</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0377940660686511</c:v>
+                  <c:v>1.03362632206403</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.016469564081258</c:v>
+                  <c:v>1.014597944623685</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.013984214594744</c:v>
+                  <c:v>1.0111667797381609</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0096278022949221</c:v>
+                  <c:v>1.007633508551379</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0058287470291081</c:v>
+                  <c:v>1.0045291261556271</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0043662211825941</c:v>
+                  <c:v>1.0033254774293481</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0033995319681801</c:v>
+                  <c:v>1.002544713937406</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.00272615629863</c:v>
+                  <c:v>1.002009694489683</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0022376572524241</c:v>
+                  <c:v>1.0016271690764871</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0018716160205241</c:v>
+                  <c:v>1.0013442570733671</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.001589991029147</c:v>
+                  <c:v>1.001129157679008</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0013684996035079</c:v>
+                  <c:v>1.0009618156212099</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.001191036851818</c:v>
+                  <c:v>1.0008290756862781</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.0010465719960751</c:v>
+                  <c:v>1.0007220184676759</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.000927339152945</c:v>
+                  <c:v>1.0006344233268341</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.0008277396594001</c:v>
+                  <c:v>1.0005618447468481</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.000743652801747</c:v>
+                  <c:v>1.000501037482179</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.000671989859828</c:v>
+                  <c:v>1.00044958771385</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.000610397901966</c:v>
+                  <c:v>1.000405669966927</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.0005570584208361</c:v>
+                  <c:v>1.000367883070816</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1252,67 +1252,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>1.1994341194934199</c:v>
+                  <c:v>1.1944551199766771</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0377940660686511</c:v>
+                  <c:v>1.03362632206403</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.016469564081258</c:v>
+                  <c:v>1.014597944623685</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.013984214594744</c:v>
+                  <c:v>1.0111667797381609</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0096278022949221</c:v>
+                  <c:v>1.007633508551379</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0058287470291081</c:v>
+                  <c:v>1.0045291261556271</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0043662211825941</c:v>
+                  <c:v>1.0033254774293481</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0033995319681801</c:v>
+                  <c:v>1.002544713937406</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.00272615629863</c:v>
+                  <c:v>1.002009694489683</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0022376572524241</c:v>
+                  <c:v>1.0016271690764871</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0018716160205241</c:v>
+                  <c:v>1.0013442570733671</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.001589991029147</c:v>
+                  <c:v>1.001129157679008</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0013684996035079</c:v>
+                  <c:v>1.0009618156212099</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.001191036851818</c:v>
+                  <c:v>1.0008290756862781</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.0010465719960751</c:v>
+                  <c:v>1.0007220184676759</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.000927339152945</c:v>
+                  <c:v>1.0006344233268341</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.0008277396594001</c:v>
+                  <c:v>1.0005618447468481</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.000743652801747</c:v>
+                  <c:v>1.000501037482179</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.000671989859828</c:v>
+                  <c:v>1.00044958771385</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.000610397901966</c:v>
+                  <c:v>1.000405669966927</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.0005570584208361</c:v>
+                  <c:v>1.000367883070816</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1349,52 +1349,52 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="5">
-                  <c:v>1.0058287470291081</c:v>
+                  <c:v>1.0045291261556271</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0043662211825941</c:v>
+                  <c:v>1.0033254774293481</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0033995319681801</c:v>
+                  <c:v>1.002544713937406</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.00272615629863</c:v>
+                  <c:v>1.002009694489683</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0022376572524241</c:v>
+                  <c:v>1.0016271690764871</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0018716160205241</c:v>
+                  <c:v>1.0013442570733671</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.001589991029147</c:v>
+                  <c:v>1.001129157679008</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0013684996035079</c:v>
+                  <c:v>1.0009618156212099</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.001191036851818</c:v>
+                  <c:v>1.0008290756862781</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.0010465719960751</c:v>
+                  <c:v>1.0007220184676759</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.000927339152945</c:v>
+                  <c:v>1.0006344233268341</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.0008277396594001</c:v>
+                  <c:v>1.0005618447468481</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.000743652801747</c:v>
+                  <c:v>1.000501037482179</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.000671989859828</c:v>
+                  <c:v>1.00044958771385</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.000610397901966</c:v>
+                  <c:v>1.000405669966927</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.0005570584208361</c:v>
+                  <c:v>1.000367883070816</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8529,22 +8529,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L122"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
@@ -8571,7 +8571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>1.1831372913937821</v>
       </c>
       <c r="D2">
-        <v>1.1994341194934199</v>
+        <v>1.1944551199766771</v>
       </c>
       <c r="F2">
         <v>1.1994341194934199</v>
@@ -8601,14 +8601,14 @@
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K22" si="0">POWER(B2-D2,2)</f>
-        <v>2.6558660610914546E-4</v>
+        <v>1.2809324383179468E-4</v>
       </c>
       <c r="L2">
         <f t="shared" ref="L2:L22" si="1">POWER(C2-F2,2)</f>
         <v>2.6558660610914546E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -8619,7 +8619,7 @@
         <v>1.002130380616937</v>
       </c>
       <c r="D3">
-        <v>1.0377940660686511</v>
+        <v>1.03362632206403</v>
       </c>
       <c r="F3">
         <v>1.0377940660686511</v>
@@ -8638,14 +8638,14 @@
       </c>
       <c r="K3">
         <f t="shared" si="0"/>
-        <v>1.2718984599988008E-3</v>
+        <v>9.9199432763871082E-4</v>
       </c>
       <c r="L3">
         <f t="shared" si="1"/>
         <v>1.2718984599988008E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -8656,7 +8656,7 @@
         <v>1.030411626703041</v>
       </c>
       <c r="D4">
-        <v>1.016469564081258</v>
+        <v>1.014597944623685</v>
       </c>
       <c r="F4">
         <v>1.016469564081258</v>
@@ -8675,14 +8675,14 @@
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>1.9438111014971843E-4</v>
+        <v>2.5007254090694391E-4</v>
       </c>
       <c r="L4">
         <f t="shared" si="1"/>
         <v>1.9438111014971843E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>1.0184990111164161</v>
       </c>
       <c r="D5">
-        <v>1.013984214594744</v>
+        <v>1.0111667797381609</v>
       </c>
       <c r="F5">
         <v>1.013984214594744</v>
@@ -8712,14 +8712,14 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>2.0383387632102331E-5</v>
+        <v>5.3761616984268921E-5</v>
       </c>
       <c r="L5">
         <f t="shared" si="1"/>
         <v>2.0383387632102331E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -8730,7 +8730,7 @@
         <v>1.0161023393365121</v>
       </c>
       <c r="D6">
-        <v>1.0096278022949221</v>
+        <v>1.007633508551379</v>
       </c>
       <c r="F6">
         <v>1.0096278022949221</v>
@@ -8749,14 +8749,14 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>4.1919629902920422E-5</v>
+        <v>7.1721094867217312E-5</v>
       </c>
       <c r="L6">
         <f t="shared" si="1"/>
         <v>4.1919629902920422E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -8767,10 +8767,10 @@
         <v>1.0136432586074671</v>
       </c>
       <c r="D7">
-        <v>1.0058287470291081</v>
+        <v>1.0045291261556271</v>
       </c>
       <c r="E7">
-        <v>1.0058287470291081</v>
+        <v>1.0045291261556271</v>
       </c>
       <c r="F7">
         <v>1.0033520851784461</v>
@@ -8789,14 +8789,14 @@
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>6.1066591208306799E-5</v>
+        <v>8.306741034968313E-5</v>
       </c>
       <c r="L7">
         <f t="shared" si="1"/>
         <v>1.0590825054618728E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -8807,10 +8807,10 @@
         <v>1.0079164241977421</v>
       </c>
       <c r="D8">
-        <v>1.0043662211825941</v>
+        <v>1.0033254774293481</v>
       </c>
       <c r="E8">
-        <v>1.0043662211825941</v>
+        <v>1.0033254774293481</v>
       </c>
       <c r="F8">
         <v>1.001655320267989</v>
@@ -8829,14 +8829,14 @@
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>1.2603941448765723E-5</v>
+        <v>2.1076792230227308E-5</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
         <v>3.9201422419169684E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -8847,10 +8847,10 @@
         <v>1.0064567403158251</v>
       </c>
       <c r="D9">
-        <v>1.0033995319681801</v>
+        <v>1.002544713937406</v>
       </c>
       <c r="E9">
-        <v>1.0033995319681801</v>
+        <v>1.002544713937406</v>
       </c>
       <c r="F9">
         <v>1.000817427077102</v>
@@ -8869,14 +8869,14 @@
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
-        <v>9.3465228809102819E-6</v>
+        <v>1.5303950385447189E-5</v>
       </c>
       <c r="L9">
         <f t="shared" si="1"/>
         <v>3.1801853804437974E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -8887,10 +8887,10 @@
         <v>1.0027301731675771</v>
       </c>
       <c r="D10">
-        <v>1.00272615629863</v>
+        <v>1.002009694489683</v>
       </c>
       <c r="E10">
-        <v>1.00272615629863</v>
+        <v>1.002009694489683</v>
       </c>
       <c r="F10">
         <v>1.0004036602700399</v>
@@ -8909,14 +8909,14 @@
       </c>
       <c r="K10">
         <f t="shared" si="0"/>
-        <v>1.6135236137541791E-11</v>
+        <v>5.1908952529994829E-7</v>
       </c>
       <c r="L10">
         <f t="shared" si="1"/>
         <v>5.4126622624067448E-6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -8927,24 +8927,24 @@
         <v>1.008385607432384</v>
       </c>
       <c r="D11">
-        <v>1.0022376572524241</v>
+        <v>1.0016271690764871</v>
       </c>
       <c r="E11">
-        <v>1.0022376572524241</v>
+        <v>1.0016271690764871</v>
       </c>
       <c r="F11">
         <v>1.0001993347396649</v>
       </c>
       <c r="K11">
         <f t="shared" si="0"/>
-        <v>3.7797291415269571E-5</v>
+        <v>4.5676489010459155E-5</v>
       </c>
       <c r="L11">
         <f t="shared" si="1"/>
         <v>6.7015060599558406E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -8955,24 +8955,24 @@
         <v>1.003344369913904</v>
       </c>
       <c r="D12">
-        <v>1.0018716160205241</v>
+        <v>1.0013442570733671</v>
       </c>
       <c r="E12">
-        <v>1.0018716160205241</v>
+        <v>1.0013442570733671</v>
       </c>
       <c r="F12">
         <v>1.0000984350984881</v>
       </c>
       <c r="K12">
         <f t="shared" si="0"/>
-        <v>2.1690040304655462E-6</v>
+        <v>4.0004513748806518E-6</v>
       </c>
       <c r="L12">
         <f t="shared" si="1"/>
         <v>1.05360928259291E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -8983,24 +8983,24 @@
         <v>0.9992579141187633</v>
       </c>
       <c r="D13">
-        <v>1.001589991029147</v>
+        <v>1.001129157679008</v>
       </c>
       <c r="E13">
-        <v>1.001589991029147</v>
+        <v>1.001129157679008</v>
       </c>
       <c r="F13">
         <v>1.000048609031374</v>
       </c>
       <c r="K13">
         <f t="shared" si="0"/>
-        <v>5.4385827159449195E-6</v>
+        <v>3.5015524617572842E-6</v>
       </c>
       <c r="L13">
         <f t="shared" si="1"/>
         <v>6.251984448285143E-7</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -9011,24 +9011,24 @@
         <v>1.0043200798648679</v>
       </c>
       <c r="D14">
-        <v>1.0013684996035079</v>
+        <v>1.0009618156212099</v>
       </c>
       <c r="E14">
-        <v>1.0013684996035079</v>
+        <v>1.0009618156212099</v>
       </c>
       <c r="F14">
         <v>1.0000240040185611</v>
       </c>
       <c r="K14">
         <f t="shared" si="0"/>
-        <v>8.7118260392499563E-6</v>
+        <v>1.1277938730232093E-5</v>
       </c>
       <c r="L14">
         <f t="shared" si="1"/>
         <v>1.8456267677221274E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -9039,24 +9039,24 @@
         <v>1.0009090932547799</v>
       </c>
       <c r="D15">
-        <v>1.001191036851818</v>
+        <v>1.0008290756862781</v>
       </c>
       <c r="E15">
-        <v>1.001191036851818</v>
+        <v>1.0008290756862781</v>
       </c>
       <c r="F15">
         <v>1.000011853618366</v>
       </c>
       <c r="K15">
         <f t="shared" si="0"/>
-        <v>7.9492191910746897E-8</v>
+        <v>6.4028112689473757E-9</v>
       </c>
       <c r="L15">
         <f t="shared" si="1"/>
         <v>8.0503896515227526E-7</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -9067,24 +9067,24 @@
         <v>1.0044375782189501</v>
       </c>
       <c r="D16">
-        <v>1.0010465719960751</v>
+        <v>1.0007220184676759</v>
       </c>
       <c r="E16">
-        <v>1.0010465719960751</v>
+        <v>1.0007220184676759</v>
       </c>
       <c r="F16">
         <v>1.000005853531067</v>
       </c>
       <c r="K16">
         <f t="shared" si="0"/>
-        <v>1.1498923203577151E-5</v>
+        <v>1.38053842652883E-5</v>
       </c>
       <c r="L16">
         <f t="shared" si="1"/>
         <v>1.9640183709192645E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -9095,24 +9095,24 @@
         <v>1.0016942872036509</v>
       </c>
       <c r="D17">
-        <v>1.000927339152945</v>
+        <v>1.0006344233268341</v>
       </c>
       <c r="E17">
-        <v>1.000927339152945</v>
+        <v>1.0006344233268341</v>
       </c>
       <c r="F17">
         <v>1.0000028905794749</v>
       </c>
       <c r="K17">
         <f t="shared" si="0"/>
-        <v>5.8820931248170937E-7</v>
+        <v>1.1233114373813302E-6</v>
       </c>
       <c r="L17">
         <f t="shared" si="1"/>
         <v>2.8608225402741581E-6</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -9123,24 +9123,24 @@
         <v>1.0005022113309909</v>
       </c>
       <c r="D18">
-        <v>1.0008277396594001</v>
+        <v>1.0005618447468481</v>
       </c>
       <c r="E18">
-        <v>1.0008277396594001</v>
+        <v>1.0005618447468481</v>
       </c>
       <c r="F18">
         <v>1.000001427420407</v>
       </c>
       <c r="K18">
         <f t="shared" si="0"/>
-        <v>1.0596869259685709E-7</v>
+        <v>3.5561442867893906E-9</v>
       </c>
       <c r="L18">
         <f t="shared" si="1"/>
         <v>2.5078452509974986E-7</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -9151,24 +9151,24 @@
         <v>1.000425774011753</v>
       </c>
       <c r="D19">
-        <v>1.000743652801747</v>
+        <v>1.000501037482179</v>
       </c>
       <c r="E19">
-        <v>1.000743652801747</v>
+        <v>1.000501037482179</v>
       </c>
       <c r="F19">
         <v>1.0000007048860049</v>
       </c>
       <c r="K19">
         <f t="shared" si="0"/>
-        <v>1.0104692512805484E-7</v>
+        <v>5.6645899805605655E-9</v>
       </c>
       <c r="L19">
         <f t="shared" si="1"/>
         <v>1.8068376166428319E-7</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -9179,24 +9179,24 @@
         <v>1.000285494341935</v>
       </c>
       <c r="D20">
-        <v>1.000671989859828</v>
+        <v>1.00044958771385</v>
       </c>
       <c r="E20">
-        <v>1.000671989859828</v>
+        <v>1.00044958771385</v>
       </c>
       <c r="F20">
         <v>1.000000348085454</v>
       </c>
       <c r="K20">
         <f t="shared" si="0"/>
-        <v>1.4937878535132994E-7</v>
+        <v>2.6926634706408116E-8</v>
       </c>
       <c r="L20">
         <f t="shared" si="1"/>
         <v>8.1308387585137921E-8</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -9207,24 +9207,24 @@
         <v>0.99887982637621764</v>
       </c>
       <c r="D21">
-        <v>1.000610397901966</v>
+        <v>1.000405669966927</v>
       </c>
       <c r="E21">
-        <v>1.000610397901966</v>
+        <v>1.000405669966927</v>
       </c>
       <c r="F21">
         <v>1.0000001718908911</v>
       </c>
       <c r="K21">
         <f t="shared" si="0"/>
-        <v>2.9948778057311565E-6</v>
+        <v>2.3281986633089459E-6</v>
       </c>
       <c r="L21">
         <f t="shared" si="1"/>
         <v>1.2551740722488897E-6</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -9235,46 +9235,46 @@
         <v>1.00011900962344</v>
       </c>
       <c r="D22">
-        <v>1.0005570584208361</v>
+        <v>1.000367883070816</v>
       </c>
       <c r="E22">
-        <v>1.0005570584208361</v>
+        <v>1.000367883070816</v>
       </c>
       <c r="F22">
         <v>1.0000000848828301</v>
       </c>
       <c r="K22">
         <f t="shared" si="0"/>
-        <v>1.9188674890013642E-7</v>
+        <v>6.1937992808818585E-8</v>
       </c>
       <c r="L22">
         <f t="shared" si="1"/>
         <v>1.4143093929138413E-8</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="D23">
-        <v>1.000510547578713</v>
+        <v>1.0003351370981499</v>
       </c>
       <c r="E23">
-        <v>1.000510547578713</v>
+        <v>1.0003351370981499</v>
       </c>
       <c r="F23">
         <v>1.0000000419166759</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="D24">
-        <v>1.000469737392746</v>
+        <v>1.0003065739494761</v>
       </c>
       <c r="E24">
-        <v>1.000469737392746</v>
+        <v>1.0003065739494761</v>
       </c>
       <c r="F24">
         <v>1.000000020699213</v>
@@ -9284,22 +9284,22 @@
       </c>
       <c r="K24">
         <f>SUM(K7:K22)</f>
-        <v>1.5284355953982607E-4</v>
+        <v>2.0178505660701691E-4</v>
       </c>
       <c r="L24">
         <f>SUM(L7:L22)</f>
         <v>3.0404494763488517E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="D25">
-        <v>1.000433724685621</v>
+        <v>1.0002815106093881</v>
       </c>
       <c r="E25">
-        <v>1.000433724685621</v>
+        <v>1.0002815106093881</v>
       </c>
       <c r="F25">
         <v>1.0000000102216451</v>
@@ -9309,1223 +9309,1223 @@
       </c>
       <c r="K25">
         <f>SQRT(K24)</f>
-        <v>1.236299152874522E-2</v>
+        <v>1.4205106708751501E-2</v>
       </c>
       <c r="L25">
         <f>SQRT(L24)</f>
         <v>1.7436884688352021E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="D26">
-        <v>1.0004017792169579</v>
+        <v>1.0002593979683689</v>
       </c>
       <c r="E26">
-        <v>1.0004017792169579</v>
+        <v>1.0002593979683689</v>
       </c>
       <c r="F26">
         <v>1.000000005047633</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="D27">
-        <v>1.0003733052887871</v>
+        <v>1.000239790515248</v>
       </c>
       <c r="E27">
-        <v>1.0003733052887871</v>
+        <v>1.000239790515248</v>
       </c>
       <c r="F27">
         <v>1.000000002492613</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="D28">
-        <v>1.000347812962092</v>
+        <v>1.000222323740267</v>
       </c>
       <c r="E28">
-        <v>1.000347812962092</v>
+        <v>1.000222323740267</v>
       </c>
       <c r="F28">
         <v>1.0000000012308969</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="D29">
-        <v>1.0003248962256071</v>
+        <v>1.000206697085811</v>
       </c>
       <c r="E29">
-        <v>1.0003248962256071</v>
+        <v>1.000206697085811</v>
       </c>
       <c r="F29">
         <v>1.0000000006078389</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="D30">
-        <v>1.000304216258822</v>
+        <v>1.0001926609412091</v>
       </c>
       <c r="E30">
-        <v>1.000304216258822</v>
+        <v>1.0001926609412091</v>
       </c>
       <c r="F30">
         <v>1.0000000003001619</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="D31">
-        <v>1.00028548847236</v>
+        <v>1.0001800066213991</v>
       </c>
       <c r="E31">
-        <v>1.00028548847236</v>
+        <v>1.0001800066213991</v>
       </c>
       <c r="F31">
         <v>1.000000000148225</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="D32">
-        <v>1.0002684723803099</v>
+        <v>1.0001685585719939</v>
       </c>
       <c r="E32">
-        <v>1.0002684723803099</v>
+        <v>1.0001685585719939</v>
       </c>
       <c r="F32">
         <v>1.0000000000731959</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
       <c r="D33">
-        <v>1.000252963617531</v>
+        <v>1.0001581682529079</v>
       </c>
       <c r="E33">
-        <v>1.000252963617531</v>
+        <v>1.0001581682529079</v>
       </c>
       <c r="F33">
         <v>1.000000000036146</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="D34">
-        <v>1.000238787597147</v>
+        <v>1.0001487092998289</v>
       </c>
       <c r="E34">
-        <v>1.000238787597147</v>
+        <v>1.0001487092998289</v>
       </c>
       <c r="F34">
         <v>1.0000000000178491</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="D35">
-        <v>1.0002257944334081</v>
+        <v>1.000140073667307</v>
       </c>
       <c r="E35">
-        <v>1.0002257944334081</v>
+        <v>1.000140073667307</v>
       </c>
       <c r="F35">
         <v>1.0000000000088141</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="D36">
-        <v>1.0002138548489381</v>
+        <v>1.000132168532301</v>
       </c>
       <c r="E36">
-        <v>1.0002138548489381</v>
+        <v>1.000132168532301</v>
       </c>
       <c r="F36">
         <v>1.000000000004353</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="D37">
-        <v>1.0002028568537411</v>
+        <v>1.000124913791542</v>
       </c>
       <c r="E37">
-        <v>1.0002028568537411</v>
+        <v>1.000124913791542</v>
       </c>
       <c r="F37">
         <v>1.0000000000021489</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
       <c r="D38">
-        <v>1.000192703033731</v>
+        <v>1.0001182400260511</v>
       </c>
       <c r="E38">
-        <v>1.000192703033731</v>
+        <v>1.0001182400260511</v>
       </c>
       <c r="F38">
         <v>1.0000000000010609</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
       <c r="D39">
-        <v>1.0001833083239791</v>
+        <v>1.0001120868357469</v>
       </c>
       <c r="E39">
-        <v>1.0001833083239791</v>
+        <v>1.0001120868357469</v>
       </c>
       <c r="F39">
         <v>1.000000000000524</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
       <c r="D40">
-        <v>1.0001745981699419</v>
+        <v>1.000106401469204</v>
       </c>
       <c r="E40">
-        <v>1.0001745981699419</v>
+        <v>1.000106401469204</v>
       </c>
       <c r="F40">
         <v>1.0000000000002589</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="D41">
-        <v>1.0001665070011601</v>
+        <v>1.0001011376902651</v>
       </c>
       <c r="E41">
-        <v>1.0001665070011601</v>
+        <v>1.0001011376902651</v>
       </c>
       <c r="F41">
         <v>1.0000000000001279</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="D42">
-        <v>1.0001589769580581</v>
+        <v>1.000096254835831</v>
       </c>
       <c r="E42">
-        <v>1.0001589769580581</v>
+        <v>1.000096254835831</v>
       </c>
       <c r="F42">
         <v>1.0000000000000631</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
       <c r="D43">
-        <v>1.000151956824926</v>
+        <v>1.0000917170288739</v>
       </c>
       <c r="E43">
-        <v>1.000151956824926</v>
+        <v>1.0000917170288739</v>
       </c>
       <c r="F43">
         <v>1.0000000000000311</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
       <c r="D44">
-        <v>1.0001454011316919</v>
+        <v>1.0000874925180949</v>
       </c>
       <c r="E44">
-        <v>1.0001454011316919</v>
+        <v>1.0000874925180949</v>
       </c>
       <c r="F44">
         <v>1.0000000000000151</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
       <c r="D45">
-        <v>1.0001392693946149</v>
+        <v>1.000083553121484</v>
       </c>
       <c r="E45">
-        <v>1.0001392693946149</v>
+        <v>1.000083553121484</v>
       </c>
       <c r="F45">
         <v>1.000000000000008</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
       <c r="D46">
-        <v>1.000133525471808</v>
+        <v>1.000079873755489</v>
       </c>
       <c r="E46">
-        <v>1.000133525471808</v>
+        <v>1.000079873755489</v>
       </c>
       <c r="F46">
         <v>1.000000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
       <c r="D47">
-        <v>1.0001281370141459</v>
+        <v>1.0000764320350859</v>
       </c>
       <c r="E47">
-        <v>1.0001281370141459</v>
+        <v>1.0000764320350859</v>
       </c>
       <c r="F47">
         <v>1.000000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
       <c r="D48">
-        <v>1.000123074995712</v>
+        <v>1.0000732079327961</v>
       </c>
       <c r="E48">
-        <v>1.000123074995712</v>
+        <v>1.0000732079327961</v>
       </c>
       <c r="F48">
         <v>1.0000000000000011</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
       <c r="D49">
-        <v>1.000118313310874</v>
+        <v>1.0000701834869219</v>
       </c>
       <c r="E49">
-        <v>1.000118313310874</v>
+        <v>1.0000701834869219</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
       <c r="D50">
-        <v>1.000113828427365</v>
+        <v>1.0000673425510631</v>
       </c>
       <c r="E50">
-        <v>1.000113828427365</v>
+        <v>1.0000673425510631</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
       <c r="D51">
-        <v>1.0001095990866431</v>
+        <v>1.00006467057835</v>
       </c>
       <c r="E51">
-        <v>1.0001095990866431</v>
+        <v>1.00006467057835</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
       <c r="D52">
-        <v>1.0001056060442759</v>
+        <v>1.0000621544350199</v>
       </c>
       <c r="E52">
-        <v>1.0001056060442759</v>
+        <v>1.0000621544350199</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
       <c r="D53">
-        <v>1.000101831844364</v>
+        <v>1.0000597822388559</v>
       </c>
       <c r="E53">
-        <v>1.000101831844364</v>
+        <v>1.0000597822388559</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
       <c r="D54">
-        <v>1.0000982606229629</v>
+        <v>1.0000575432187679</v>
       </c>
       <c r="E54">
-        <v>1.0000982606229629</v>
+        <v>1.0000575432187679</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
       <c r="D55">
-        <v>1.0000948779363359</v>
+        <v>1.0000554275924149</v>
       </c>
       <c r="E55">
-        <v>1.0000948779363359</v>
+        <v>1.0000554275924149</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
       <c r="D56">
-        <v>1.000091670610489</v>
+        <v>1.0000534264592671</v>
       </c>
       <c r="E56">
-        <v>1.000091670610489</v>
+        <v>1.0000534264592671</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
       <c r="D57">
-        <v>1.0000886266090361</v>
+        <v>1.0000515317069241</v>
       </c>
       <c r="E57">
-        <v>1.0000886266090361</v>
+        <v>1.0000515317069241</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
       <c r="D58">
-        <v>1.0000857349168719</v>
+        <v>1.0000497359288361</v>
       </c>
       <c r="E58">
-        <v>1.0000857349168719</v>
+        <v>1.0000497359288361</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
       <c r="D59">
-        <v>1.0000829854375271</v>
+        <v>1.000048032351879</v>
       </c>
       <c r="E59">
-        <v>1.0000829854375271</v>
+        <v>1.000048032351879</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
       <c r="D60">
-        <v>1.000080368902396</v>
+        <v>1.000046414772447</v>
       </c>
       <c r="E60">
-        <v>1.000080368902396</v>
+        <v>1.000046414772447</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
       <c r="D61">
-        <v>1.0000778767902789</v>
+        <v>1.00004487749995</v>
       </c>
       <c r="E61">
-        <v>1.0000778767902789</v>
+        <v>1.00004487749995</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
       <c r="D62">
-        <v>1.0000755012559359</v>
+        <v>1.000043415306735</v>
       </c>
       <c r="E62">
-        <v>1.0000755012559359</v>
+        <v>1.000043415306735</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
       <c r="D63">
-        <v>1.000073235066496</v>
+        <v>1.000042023383626</v>
       </c>
       <c r="E63">
-        <v>1.000073235066496</v>
+        <v>1.000042023383626</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
       <c r="D64">
-        <v>1.0000710715447629</v>
+        <v>1.000040697300363</v>
       </c>
       <c r="E64">
-        <v>1.0000710715447629</v>
+        <v>1.000040697300363</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
       <c r="D65">
-        <v>1.0000690045185641</v>
+        <v>1.000039432970337</v>
       </c>
       <c r="E65">
-        <v>1.0000690045185641</v>
+        <v>1.000039432970337</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
       <c r="D66">
-        <v>1.000067028275422</v>
+        <v>1.000038226619095</v>
       </c>
       <c r="E66">
-        <v>1.000067028275422</v>
+        <v>1.000038226619095</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
       <c r="D67">
-        <v>1.000065137521913</v>
+        <v>1.0000370747561611</v>
       </c>
       <c r="E67">
-        <v>1.000065137521913</v>
+        <v>1.0000370747561611</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
       <c r="D68">
-        <v>1.000063327347172</v>
+        <v>1.0000359741497831</v>
       </c>
       <c r="E68">
-        <v>1.000063327347172</v>
+        <v>1.0000359741497831</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
       <c r="D69">
-        <v>1.0000615931900561</v>
+        <v>1.0000349218042579</v>
       </c>
       <c r="E69">
-        <v>1.0000615931900561</v>
+        <v>1.0000349218042579</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
       <c r="D70">
-        <v>1.000059930809565</v>
+        <v>1.0000339149395421</v>
       </c>
       <c r="E70">
-        <v>1.000059930809565</v>
+        <v>1.0000339149395421</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
       <c r="D71">
-        <v>1.000058336258145</v>
+        <v>1.00003295097289</v>
       </c>
       <c r="E71">
-        <v>1.000058336258145</v>
+        <v>1.00003295097289</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
       <c r="D72">
-        <v>1.0000568058575621</v>
+        <v>1.000032027502288</v>
       </c>
       <c r="E72">
-        <v>1.0000568058575621</v>
+        <v>1.000032027502288</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
       <c r="D73">
-        <v>1.000055336177061</v>
+        <v>1.00003114229149</v>
       </c>
       <c r="E73">
-        <v>1.000055336177061</v>
+        <v>1.00003114229149</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
       <c r="D74">
-        <v>1.000053924013578</v>
+        <v>1.0000302932564771</v>
       </c>
       <c r="E74">
-        <v>1.000053924013578</v>
+        <v>1.0000302932564771</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
       <c r="D75">
-        <v>1.000052566373766</v>
+        <v>1.0000294784531929</v>
       </c>
       <c r="E75">
-        <v>1.000052566373766</v>
+        <v>1.0000294784531929</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
       <c r="D76">
-        <v>1.000051260457673</v>
+        <v>1.0000286960664131</v>
       </c>
       <c r="E76">
-        <v>1.000051260457673</v>
+        <v>1.0000286960664131</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
       <c r="D77">
-        <v>1.0000500036438771</v>
+        <v>1.0000279443996369</v>
       </c>
       <c r="E77">
-        <v>1.0000500036438771</v>
+        <v>1.0000279443996369</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
       <c r="D78">
-        <v>1.0000487934759461</v>
+        <v>1.000027221865891</v>
       </c>
       <c r="E78">
-        <v>1.0000487934759461</v>
+        <v>1.000027221865891</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
       <c r="D79">
-        <v>1.0000476276500809</v>
+        <v>1.0000265269793509</v>
       </c>
       <c r="E79">
-        <v>1.0000476276500809</v>
+        <v>1.0000265269793509</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
       <c r="D80">
-        <v>1.000046504003834</v>
+        <v>1.0000258583477071</v>
       </c>
       <c r="E80">
-        <v>1.000046504003834</v>
+        <v>1.0000258583477071</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
       <c r="D81">
-        <v>1.0000454205057809</v>
+        <v>1.000025214665186</v>
       </c>
       <c r="E81">
-        <v>1.0000454205057809</v>
+        <v>1.000025214665186</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
       <c r="D82">
-        <v>1.0000443752460779</v>
+        <v>1.000024594706181</v>
       </c>
       <c r="E82">
-        <v>1.0000443752460779</v>
+        <v>1.000024594706181</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
       <c r="D83">
-        <v>1.0000433664277919</v>
+        <v>1.0000239973194129</v>
       </c>
       <c r="E83">
-        <v>1.0000433664277919</v>
+        <v>1.0000239973194129</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
       <c r="D84">
-        <v>1.0000423923589561</v>
+        <v>1.0000234214225949</v>
       </c>
       <c r="E84">
-        <v>1.0000423923589561</v>
+        <v>1.0000234214225949</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
       <c r="D85">
-        <v>1.000041451445266</v>
+        <v>1.000022865997521</v>
       </c>
       <c r="E85">
-        <v>1.000041451445266</v>
+        <v>1.000022865997521</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
       <c r="D86">
-        <v>1.00004054218337</v>
+        <v>1.000022330085574</v>
       </c>
       <c r="E86">
-        <v>1.00004054218337</v>
+        <v>1.000022330085574</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
       <c r="D87">
-        <v>1.000039663154682</v>
+        <v>1.0000218127835849</v>
       </c>
       <c r="E87">
-        <v>1.000039663154682</v>
+        <v>1.0000218127835849</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
       <c r="D88">
-        <v>1.00003881301969</v>
+        <v>1.000021313240034</v>
       </c>
       <c r="E88">
-        <v>1.00003881301969</v>
+        <v>1.000021313240034</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
       <c r="D89">
-        <v>1.0000379905127059</v>
+        <v>1.0000208306515399</v>
       </c>
       <c r="E89">
-        <v>1.0000379905127059</v>
+        <v>1.0000208306515399</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
       <c r="D90">
-        <v>1.0000371944370161</v>
+        <v>1.000020364259639</v>
       </c>
       <c r="E90">
-        <v>1.0000371944370161</v>
+        <v>1.000020364259639</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
       <c r="D91">
-        <v>1.000036423660398</v>
+        <v>1.0000199133477989</v>
       </c>
       <c r="E91">
-        <v>1.000036423660398</v>
+        <v>1.0000199133477989</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
       <c r="D92">
-        <v>1.0000356771109851</v>
+        <v>1.000019477238671</v>
       </c>
       <c r="E92">
-        <v>1.0000356771109851</v>
+        <v>1.000019477238671</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
       <c r="D93">
-        <v>1.000034953773423</v>
+        <v>1.0000190552915449</v>
       </c>
       <c r="E93">
-        <v>1.000034953773423</v>
+        <v>1.0000190552915449</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
       <c r="D94">
-        <v>1.0000342526853221</v>
+        <v>1.0000186469000001</v>
       </c>
       <c r="E94">
-        <v>1.0000342526853221</v>
+        <v>1.0000186469000001</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
       <c r="D95">
-        <v>1.0000335729339631</v>
+        <v>1.000018251489722</v>
       </c>
       <c r="E95">
-        <v>1.0000335729339631</v>
+        <v>1.000018251489722</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
       <c r="D96">
-        <v>1.0000329136532371</v>
+        <v>1.0000178685164891</v>
       </c>
       <c r="E96">
-        <v>1.0000329136532371</v>
+        <v>1.0000178685164891</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
       <c r="D97">
-        <v>1.000032274020811</v>
+        <v>1.000017497464295</v>
       </c>
       <c r="E97">
-        <v>1.000032274020811</v>
+        <v>1.000017497464295</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
       <c r="D98">
-        <v>1.000031653255482</v>
+        <v>1.000017137843618</v>
       </c>
       <c r="E98">
-        <v>1.000031653255482</v>
+        <v>1.000017137843618</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
       <c r="D99">
-        <v>1.0000310506147321</v>
+        <v>1.0000167891898</v>
       </c>
       <c r="E99">
-        <v>1.0000310506147321</v>
+        <v>1.0000167891898</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
       <c r="D100">
-        <v>1.0000304653924339</v>
+        <v>1.0000164510615519</v>
       </c>
       <c r="E100">
-        <v>1.0000304653924339</v>
+        <v>1.0000164510615519</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
       <c r="D101">
-        <v>1.0000298969167289</v>
+        <v>1.000016123039553</v>
       </c>
       <c r="E101">
-        <v>1.0000298969167289</v>
+        <v>1.000016123039553</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
       <c r="D102">
-        <v>1.0000293445480399</v>
+        <v>1.0000158047251559</v>
       </c>
       <c r="E102">
-        <v>1.0000293445480399</v>
+        <v>1.0000158047251559</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
       <c r="D103">
-        <v>1.0000288076772219</v>
+        <v>1.000015495739172</v>
       </c>
       <c r="E103">
-        <v>1.0000288076772219</v>
+        <v>1.000015495739172</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
       <c r="D104">
-        <v>1.000028285723831</v>
+        <v>1.0000151957207459</v>
       </c>
       <c r="E104">
-        <v>1.000028285723831</v>
+        <v>1.0000151957207459</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
       <c r="D105">
-        <v>1.000027778134513</v>
+        <v>1.0000149043262989</v>
       </c>
       <c r="E105">
-        <v>1.000027778134513</v>
+        <v>1.0000149043262989</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
       <c r="D106">
-        <v>1.000027284381495</v>
+        <v>1.000014621228549</v>
       </c>
       <c r="E106">
-        <v>1.000027284381495</v>
+        <v>1.000014621228549</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -10539,21 +10539,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12084E6B-ED10-419E-8AF8-76B61C618EAB}">
   <dimension ref="A1:L122"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
@@ -10580,7 +10580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -10617,7 +10617,7 @@
         <v>2.1182610294789617E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -10654,7 +10654,7 @@
         <v>2.0172791238816843E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>1.2425133856325106E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -10728,7 +10728,7 @@
         <v>5.8386345567139819E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -10765,7 +10765,7 @@
         <v>2.7430678430166976E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>3.4829826679781342E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -10845,7 +10845,7 @@
         <v>5.0614687806103075E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -10885,7 +10885,7 @@
         <v>3.1765644933125795E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -10925,7 +10925,7 @@
         <v>3.2166543175800256E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>8.2823633460340888E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>3.3917903961416794E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -11009,7 +11009,7 @@
         <v>3.3226839507180173E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>4.0798934835907503E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -11065,7 +11065,7 @@
         <v>2.3874062340114969E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -11093,7 +11093,7 @@
         <v>8.9936511000061068E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -11121,7 +11121,7 @@
         <v>1.1608699312070515E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v>1.3372639414461234E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -11177,7 +11177,7 @@
         <v>1.473344587746152E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>7.778188148671597E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -11233,7 +11233,7 @@
         <v>6.4576491204787084E-6</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>3.3649818954190128E-8</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -11275,7 +11275,7 @@
         <v>1.0000115481240699</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -11300,7 +11300,7 @@
         <v>7.5215819367999825E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>8.6727054237994164E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>1.0000025473613601</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>1.0000015391593871</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -11367,7 +11367,7 @@
         <v>1.000000929986478</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -11381,7 +11381,7 @@
         <v>1.0000005619137671</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>1.000000339517928</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -11409,7 +11409,7 @@
         <v>1.0000002051425501</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -11423,7 +11423,7 @@
         <v>1.000000123950644</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -11437,7 +11437,7 @@
         <v>1.0000000748931031</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>1.0000000452516959</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>1.000000027341851</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -11479,7 +11479,7 @@
         <v>1.000000016520415</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -11493,7 +11493,7 @@
         <v>1.000000009981918</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -11507,7 +11507,7 @@
         <v>1.0000000060312459</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>1.0000000036441821</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -11535,7 +11535,7 @@
         <v>1.0000000022018769</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -11549,7 +11549,7 @@
         <v>1.000000001330412</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -11563,7 +11563,7 @@
         <v>1.0000000008038581</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -11577,7 +11577,7 @@
         <v>1.000000000485705</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -11591,7 +11591,7 @@
         <v>1.000000000293471</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -11605,7 +11605,7 @@
         <v>1.0000000001773199</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -11619,7 +11619,7 @@
         <v>1.0000000001071401</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>1.000000000064736</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -11647,7 +11647,7 @@
         <v>1.000000000039114</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>1.000000000023634</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -11675,7 +11675,7 @@
         <v>1.0000000000142799</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -11689,7 +11689,7 @@
         <v>1.000000000008628</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>1.0000000000052129</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -11717,7 +11717,7 @@
         <v>1.0000000000031499</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -11731,7 +11731,7 @@
         <v>1.0000000000019029</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -11745,7 +11745,7 @@
         <v>1.00000000000115</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -11759,7 +11759,7 @@
         <v>1.000000000000695</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -11773,7 +11773,7 @@
         <v>1.0000000000004201</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>1.000000000000254</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -11801,7 +11801,7 @@
         <v>1.000000000000153</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -11815,7 +11815,7 @@
         <v>1.000000000000093</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -11829,7 +11829,7 @@
         <v>1.000000000000056</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -11843,7 +11843,7 @@
         <v>1.000000000000034</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -11857,7 +11857,7 @@
         <v>1.00000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>1.000000000000012</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>1.000000000000008</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -11899,7 +11899,7 @@
         <v>1.000000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -11913,7 +11913,7 @@
         <v>1.0000000000000031</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -11927,7 +11927,7 @@
         <v>1.000000000000002</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>1.0000000000000011</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>1.0000000000000011</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -11969,7 +11969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -11997,7 +11997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -12011,7 +12011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -12039,7 +12039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -12067,7 +12067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -12095,7 +12095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -12109,7 +12109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -12123,7 +12123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -12137,7 +12137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -12179,7 +12179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -12193,7 +12193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -12221,7 +12221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -12249,7 +12249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -12263,7 +12263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -12291,7 +12291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -12305,7 +12305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -12319,7 +12319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -12347,7 +12347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -12375,7 +12375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -12389,7 +12389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -12417,7 +12417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -12431,7 +12431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -12459,82 +12459,82 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -12548,19 +12548,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BAAE3EB-31E2-4B95-86C2-DF9BC9CC5789}">
   <dimension ref="A1:L122"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12587,7 +12587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>6.6607764733575773E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -12661,7 +12661,7 @@
         <v>8.0791089880284644E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -12698,7 +12698,7 @@
         <v>1.4069850094017373E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>1.8447609181253345E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -12772,7 +12772,7 @@
         <v>4.3966524136524356E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -12812,7 +12812,7 @@
         <v>2.5903657239137158E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>3.7190708814997E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -12892,7 +12892,7 @@
         <v>4.4001285431778577E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -12932,7 +12932,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -12960,7 +12960,7 @@
         <v>5.1253898842222383E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -12988,7 +12988,7 @@
         <v>1.6451081456843016E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -13016,7 +13016,7 @@
         <v>6.6211784855391771E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -13044,7 +13044,7 @@
         <v>8.7507789651289534E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -13072,7 +13072,7 @@
         <v>3.4196761136810753E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -13100,7 +13100,7 @@
         <v>2.8040098813455356E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -13128,7 +13128,7 @@
         <v>1.9342761641743146E-5</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -13156,7 +13156,7 @@
         <v>2.6479292957942436E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -13184,7 +13184,7 @@
         <v>7.4916118488748497E-6</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>5.9507084676046163E-6</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -13240,7 +13240,7 @@
         <v>1.8716152957518606E-7</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -13268,7 +13268,7 @@
         <v>1.8204609100032936E-7</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -13282,7 +13282,7 @@
         <v>1.0000027873129329</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -13307,7 +13307,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -13332,7 +13332,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -13346,7 +13346,7 @@
         <v>1.000000490197078</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -13360,7 +13360,7 @@
         <v>1.000000274641216</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -13374,7 +13374,7 @@
         <v>1.0000001538723939</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -13388,7 +13388,7 @@
         <v>1.000000086209615</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -13402,7 +13402,7 @@
         <v>1.000000048300397</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>1.000000027061116</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -13430,7 +13430,7 @@
         <v>1.000000015161449</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -13444,7 +13444,7 @@
         <v>1.000000008494458</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -13458,7 +13458,7 @@
         <v>1.000000004759164</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -13472,7 +13472,7 @@
         <v>1.000000002666402</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -13486,7 +13486,7 @@
         <v>1.000000001493897</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -13500,7 +13500,7 @@
         <v>1.0000000008369809</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -13514,7 +13514,7 @@
         <v>1.0000000004689329</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>1.0000000002627281</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>1.000000000147198</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -13556,7 +13556,7 @@
         <v>1.00000000008247</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -13570,7 +13570,7 @@
         <v>1.000000000046205</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -13584,7 +13584,7 @@
         <v>1.0000000000258871</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v>1.000000000014504</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -13612,7 +13612,7 @@
         <v>1.0000000000081259</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -13626,7 +13626,7 @@
         <v>1.000000000004553</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>1.0000000000025511</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -13654,7 +13654,7 @@
         <v>1.0000000000014291</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -13668,7 +13668,7 @@
         <v>1.0000000000008009</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -13682,7 +13682,7 @@
         <v>1.000000000000449</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -13696,7 +13696,7 @@
         <v>1.0000000000002509</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -13710,7 +13710,7 @@
         <v>1.000000000000141</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>1.000000000000079</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -13738,7 +13738,7 @@
         <v>1.000000000000044</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>1.0000000000000251</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -13766,7 +13766,7 @@
         <v>1.000000000000014</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -13780,7 +13780,7 @@
         <v>1.000000000000008</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>1.000000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -13808,7 +13808,7 @@
         <v>1.000000000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>1.0000000000000011</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -13836,7 +13836,7 @@
         <v>1.0000000000000011</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -13850,7 +13850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -13864,7 +13864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -13878,7 +13878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -13920,7 +13920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -13934,7 +13934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -13948,7 +13948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -13976,7 +13976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -13990,7 +13990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -14018,7 +14018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -14032,7 +14032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -14046,7 +14046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -14060,7 +14060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -14074,7 +14074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -14116,7 +14116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -14130,7 +14130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -14186,7 +14186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -14242,7 +14242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -14270,7 +14270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -14284,7 +14284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -14298,7 +14298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -14312,7 +14312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -14326,7 +14326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -14354,7 +14354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -14368,7 +14368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -14382,7 +14382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -14396,7 +14396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -14410,7 +14410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -14424,7 +14424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -14438,7 +14438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -14452,7 +14452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>1.0000000000000251</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -14494,7 +14494,7 @@
         <v>1.0000000000000191</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>1.000000000000014</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -14522,7 +14522,7 @@
         <v>1.00000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -14536,7 +14536,7 @@
         <v>1.000000000000008</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -14550,7 +14550,7 @@
         <v>1.000000000000006</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>1.000000000000004</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -14578,7 +14578,7 @@
         <v>1.0000000000000031</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>1.000000000000002</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -14606,7 +14606,7 @@
         <v>1.000000000000002</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -14620,7 +14620,7 @@
         <v>1.0000000000000011</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>1.0000000000000011</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -14648,7 +14648,7 @@
         <v>1.0000000000000011</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -14662,7 +14662,7 @@
         <v>1.0000000000000011</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -14676,7 +14676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
